--- a/notebooks/test_output/cv_results_no_load.xlsx
+++ b/notebooks/test_output/cv_results_no_load.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8944444444444445</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02576005137637695</v>
+        <v>0.05270462766947298</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>34.72213949244264</v>
+        <v>11.06796971058973</v>
       </c>
       <c r="G2" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +542,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -568,7 +568,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9027777777777778</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
         <v>33.33333333333333</v>
@@ -659,7 +659,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>33.33333333333333</v>
@@ -675,7 +675,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>33.33333333333333</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-04 17:54:29</t>
+          <t>2025-11-29 12:24:27</t>
         </is>
       </c>
     </row>
